--- a/phd macro ii/spring2026/exam/Grading.xlsx
+++ b/phd macro ii/spring2026/exam/Grading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eriob421\Documents\GitHub\teaching_private\phd macro ii\spring2026\exam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B3CB2F-4FD3-44AE-BB0D-B0649CC34974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E360CCA-0126-4F46-870D-BBF24CAC85FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5007,16 +5007,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="C10" s="14">
+        <v>6</v>
+      </c>
+      <c r="D10" s="14">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>6</v>
+      </c>
       <c r="F10" s="13">
         <f>SUM(B10:E10)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G10" s="36">
         <f t="shared" ref="G10:G16" si="0">F10/70*100</f>
-        <v>0</v>
+        <v>22.857142857142858</v>
       </c>
       <c r="H10" s="29" t="str">
         <f>IF(F10&gt;59.9,"VG",IF(F10&gt;29.9,"G","U"))</f>
@@ -5066,16 +5072,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="C12" s="14">
+        <v>5</v>
+      </c>
+      <c r="D12" s="14">
+        <v>5</v>
+      </c>
+      <c r="E12" s="14">
+        <v>6</v>
+      </c>
       <c r="F12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G12" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.857142857142858</v>
       </c>
       <c r="H12" s="29" t="str">
         <f t="shared" si="2"/>
@@ -5101,16 +5113,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="C13" s="14">
+        <v>5</v>
+      </c>
+      <c r="D13" s="14">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14">
+        <v>4</v>
+      </c>
       <c r="F13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G13" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.285714285714285</v>
       </c>
       <c r="H13" s="29" t="str">
         <f t="shared" si="2"/>
@@ -5125,16 +5143,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>5</v>
+      </c>
+      <c r="E14" s="14">
+        <v>3</v>
+      </c>
       <c r="F14" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12.857142857142856</v>
       </c>
       <c r="H14" s="29" t="str">
         <f t="shared" si="2"/>
@@ -5160,12 +5184,27 @@
         <v>6</v>
       </c>
       <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="29"/>
+      <c r="C15" s="14">
+        <v>5</v>
+      </c>
+      <c r="D15" s="14">
+        <v>5</v>
+      </c>
+      <c r="E15" s="14">
+        <v>6</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G15" s="36">
+        <f t="shared" si="0"/>
+        <v>22.857142857142858</v>
+      </c>
+      <c r="H15" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>U</v>
+      </c>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15" s="9"/>
@@ -5184,16 +5223,22 @@
         <v>7</v>
       </c>
       <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>4</v>
+      </c>
       <c r="F16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="H16" s="29" t="str">
         <f t="shared" si="2"/>
@@ -5244,25 +5289,25 @@
         <f t="shared" ref="B18:G18" si="3">AVERAGE(B10:B16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C18" s="25" t="e">
+      <c r="C18" s="25">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D18" s="25" t="e">
+        <v>4</v>
+      </c>
+      <c r="D18" s="25">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E18" s="25" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="E18" s="25">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.428571428571429</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16.326530612244898</v>
       </c>
       <c r="H18" s="29" t="str">
         <f t="shared" si="2"/>
@@ -5289,17 +5334,17 @@
         <f>B18/B8*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C19" s="28" t="e">
+      <c r="C19" s="28">
         <f t="shared" ref="C19:E19" si="4">C18/C8*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" s="28" t="e">
+        <v>20</v>
+      </c>
+      <c r="D19" s="28">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="28" t="e">
+        <v>30</v>
+      </c>
+      <c r="E19" s="28">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="28"/>
